--- a/Liceo/lectura_3BCH.xlsx
+++ b/Liceo/lectura_3BCH.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="TI" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="TII" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="crudo" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F233"/>
+  <dimension ref="A1:F219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,12 +467,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>INSCUALT1</t>
+          <t>INSCUALT2</t>
         </is>
       </c>
     </row>
@@ -494,12 +494,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>EQUINSUT1</t>
+          <t>EQUINSUT2</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -551,12 +551,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EQUICALNSUT1</t>
+          <t>EQUICALNSUT2</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -581,12 +581,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EXAT1</t>
+          <t>EXAT2</t>
         </is>
       </c>
     </row>
@@ -608,13 +608,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EQUIEXAT1</t>
-        </is>
+          <t>CALEXAT2</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -635,16 +638,13 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
-        <v>30</v>
+          <t>EQUIEXAT2</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -665,16 +665,13 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>EQUICALEXAT1</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>30</v>
+          <t>PROMTRIT2</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -695,12 +692,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>PROMTRIT1</t>
+          <t>EQUICALPROMTR2</t>
         </is>
       </c>
     </row>
@@ -712,22 +709,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+          <t>CAS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2242</t>
+          <t>2246</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>EQUICALPROMTR1</t>
+          <t>INSCUALT2</t>
         </is>
       </c>
     </row>
@@ -749,12 +746,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>INSCUALT1</t>
+          <t>EQUINSUT2</t>
         </is>
       </c>
     </row>
@@ -776,13 +773,16 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EQUINSUT1</t>
-        </is>
+          <t>CALINST1</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="14">
@@ -803,12 +803,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CALINST1</t>
+          <t>EQUICALNSUT2</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -833,16 +833,13 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>EQUICALNSUT1</t>
-        </is>
-      </c>
-      <c r="F15" t="n">
-        <v>70</v>
+          <t>EXAT2</t>
+        </is>
       </c>
     </row>
     <row r="16">
@@ -863,13 +860,16 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EXAT1</t>
-        </is>
+          <t>CALEXAT2</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -890,12 +890,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EQUIEXAT1</t>
+          <t>EQUIEXAT2</t>
         </is>
       </c>
     </row>
@@ -917,16 +917,13 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>30</v>
+          <t>PROMTRIT2</t>
+        </is>
       </c>
     </row>
     <row r="19">
@@ -947,16 +944,13 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>EQUICALEXAT1</t>
-        </is>
-      </c>
-      <c r="F19" t="n">
-        <v>30</v>
+          <t>EQUICALPROMTR2</t>
+        </is>
       </c>
     </row>
     <row r="20">
@@ -967,22 +961,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CAS</t>
+          <t>COMPORTAMIENTO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2142</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>PROMTRIT1</t>
+          <t>INSCUALT2</t>
         </is>
       </c>
     </row>
@@ -994,23 +988,26 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CAS</t>
+          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>EQUICALPROMTR1</t>
-        </is>
+          <t>ACTCT2</t>
+        </is>
+      </c>
+      <c r="F21" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="22">
@@ -1021,23 +1018,26 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>COMPORTAMIENTO</t>
+          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2142</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>INSCUALT1</t>
-        </is>
+          <t>DEBT2</t>
+        </is>
+      </c>
+      <c r="F22" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="23">
@@ -1058,12 +1058,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>ACTCT1</t>
+          <t>TRAGIT2</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>DEBT1</t>
+          <t>LECT2</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>TRAGIT1</t>
+          <t>APT2</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1148,16 +1148,16 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LECT1</t>
+          <t>CALINST2</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="27">
@@ -1178,16 +1178,13 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>APT1</t>
-        </is>
-      </c>
-      <c r="F27" t="n">
-        <v>20</v>
+          <t>EXAT2</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -1208,16 +1205,16 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29">
@@ -1238,16 +1235,13 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CALINST1</t>
-        </is>
-      </c>
-      <c r="F29" t="n">
-        <v>70</v>
+          <t>PROMTRI2</t>
+        </is>
       </c>
     </row>
     <row r="30">
@@ -1258,23 +1252,26 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+          <t>English B NS IB</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>EXAT1</t>
-        </is>
+          <t>ACTCT2</t>
+        </is>
+      </c>
+      <c r="F30" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="31">
@@ -1285,26 +1282,26 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+          <t>English B NS IB</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
+          <t>DEBT2</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32">
@@ -1315,23 +1312,26 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+          <t>English B NS IB</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>PROMTRI1</t>
-        </is>
+          <t>TRAGIT2</t>
+        </is>
+      </c>
+      <c r="F32" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="33">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ACTCT1</t>
+          <t>LECT2</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -1382,12 +1382,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>DEBT1</t>
+          <t>APT2</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -1412,16 +1412,16 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>TRAGIT1</t>
+          <t>CALINST2</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36">
@@ -1442,16 +1442,13 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LECT1</t>
-        </is>
-      </c>
-      <c r="F36" t="n">
-        <v>20</v>
+          <t>EXAT2</t>
+        </is>
       </c>
     </row>
     <row r="37">
@@ -1472,16 +1469,16 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>APT1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="38">
@@ -1502,16 +1499,13 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
-        </is>
-      </c>
-      <c r="F38" t="n">
-        <v>70</v>
+          <t>PROMTRI2</t>
+        </is>
       </c>
     </row>
     <row r="39">
@@ -1522,26 +1516,26 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>English B NS IB</t>
+          <t>FÍSICA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CALINST1</t>
+          <t>ACTCT2</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="40">
@@ -1552,23 +1546,26 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>English B NS IB</t>
+          <t>FÍSICA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>EXAT1</t>
-        </is>
+          <t>DEBT2</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="41">
@@ -1579,26 +1576,26 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>English B NS IB</t>
+          <t>FÍSICA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
+          <t>TRAGIT2</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
@@ -1609,23 +1606,26 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>English B NS IB</t>
+          <t>FÍSICA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>PROMTRI1</t>
-        </is>
+          <t>LECT2</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="43">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>ACTCT1</t>
+          <t>APT2</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1676,16 +1676,16 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>DEBT1</t>
+          <t>CALINST2</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="45">
@@ -1706,16 +1706,13 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>TRAGIT1</t>
-        </is>
-      </c>
-      <c r="F45" t="n">
-        <v>20</v>
+          <t>EXAT2</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -1736,16 +1733,16 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>LECT1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="47">
@@ -1766,16 +1763,13 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>APT1</t>
-        </is>
-      </c>
-      <c r="F47" t="n">
-        <v>20</v>
+          <t>PROMTRI2</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -1786,26 +1780,26 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FÍSICA</t>
+          <t>History NS IB</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
+          <t>ACTCT2</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49">
@@ -1816,26 +1810,26 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FÍSICA</t>
+          <t>History NS IB</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>CALINST1</t>
+          <t>DEBT2</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
@@ -1846,23 +1840,26 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FÍSICA</t>
+          <t>History NS IB</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>EXAT1</t>
-        </is>
+          <t>TRAGIT2</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="51">
@@ -1873,26 +1870,26 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FÍSICA</t>
+          <t>History NS IB</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
+          <t>LECT2</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
@@ -1903,23 +1900,26 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FÍSICA</t>
+          <t>History NS IB</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2289</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>PROMTRI1</t>
-        </is>
+          <t>APT2</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="53">
@@ -1940,16 +1940,16 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ACTCT1</t>
+          <t>CALINST2</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="54">
@@ -1970,16 +1970,13 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>DEBT1</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>20</v>
+          <t>EXAT2</t>
+        </is>
       </c>
     </row>
     <row r="55">
@@ -2000,16 +1997,16 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>TRAGIT1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="56">
@@ -2030,16 +2027,13 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>LECT1</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>20</v>
+          <t>PROMTRI2</t>
+        </is>
       </c>
     </row>
     <row r="57">
@@ -2050,22 +2044,22 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>History NS IB</t>
+          <t>Lengua A: Lengua y Literatura NS IB</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>APT1</t>
+          <t>ACTCT2</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2080,26 +2074,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>History NS IB</t>
+          <t>Lengua A: Lengua y Literatura NS IB</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
+          <t>DEBT2</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59">
@@ -2110,26 +2104,26 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>History NS IB</t>
+          <t>Lengua A: Lengua y Literatura NS IB</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CALINST1</t>
+          <t>TRAGIT2</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="60">
@@ -2140,23 +2134,26 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>History NS IB</t>
+          <t>Lengua A: Lengua y Literatura NS IB</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>EXAT1</t>
-        </is>
+          <t>LECT2</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="61">
@@ -2167,26 +2164,26 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>History NS IB</t>
+          <t>Lengua A: Lengua y Literatura NS IB</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
+          <t>APT2</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62">
@@ -2197,23 +2194,26 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>History NS IB</t>
+          <t>Lengua A: Lengua y Literatura NS IB</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2289</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>PROMTRI1</t>
-        </is>
+          <t>CALINST2</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="63">
@@ -2234,16 +2234,13 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ACTCT1</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>20</v>
+          <t>EXAT2</t>
+        </is>
       </c>
     </row>
     <row r="64">
@@ -2264,16 +2261,16 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>DEBT1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65">
@@ -2294,16 +2291,13 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>TRAGIT1</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>20</v>
+          <t>PROMTRI2</t>
+        </is>
       </c>
     </row>
     <row r="66">
@@ -2314,22 +2308,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lengua A: Lengua y Literatura NS IB</t>
+          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>LECT1</t>
+          <t>ACTCT2</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -2344,22 +2338,22 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Lengua A: Lengua y Literatura NS IB</t>
+          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>APT1</t>
+          <t>DEBT2</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -2374,26 +2368,26 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Lengua A: Lengua y Literatura NS IB</t>
+          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
+          <t>TRAGIT2</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="69">
@@ -2404,26 +2398,26 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Lengua A: Lengua y Literatura NS IB</t>
+          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>CALINST1</t>
+          <t>LECT2</t>
         </is>
       </c>
       <c r="F69" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70">
@@ -2434,23 +2428,26 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Lengua A: Lengua y Literatura NS IB</t>
+          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>EXAT1</t>
-        </is>
+          <t>APT2</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="71">
@@ -2461,26 +2458,26 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lengua A: Lengua y Literatura NS IB</t>
+          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
+          <t>CALINST2</t>
         </is>
       </c>
       <c r="F71" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="72">
@@ -2491,22 +2488,22 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Lengua A: Lengua y Literatura NS IB</t>
+          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>PROMTRI1</t>
+          <t>EXAT2</t>
         </is>
       </c>
     </row>
@@ -2528,16 +2525,16 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ACTCT1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F73" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="74">
@@ -2558,16 +2555,13 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>DEBT1</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>20</v>
+          <t>PROMTRI2</t>
+        </is>
       </c>
     </row>
     <row r="75">
@@ -2578,22 +2572,22 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
+          <t>QUÍMICA</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>TRAGIT1</t>
+          <t>ACTCT2</t>
         </is>
       </c>
       <c r="F75" t="n">
@@ -2608,22 +2602,22 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
+          <t>QUÍMICA</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>LECT1</t>
+          <t>DEBT2</t>
         </is>
       </c>
       <c r="F76" t="n">
@@ -2638,22 +2632,22 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
+          <t>QUÍMICA</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>APT1</t>
+          <t>TRAGIT2</t>
         </is>
       </c>
       <c r="F77" t="n">
@@ -2668,26 +2662,26 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
+          <t>QUÍMICA</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
+          <t>LECT2</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79">
@@ -2698,26 +2692,26 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
+          <t>QUÍMICA</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>CALINST1</t>
+          <t>APT2</t>
         </is>
       </c>
       <c r="F79" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="80">
@@ -2728,23 +2722,26 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
+          <t>QUÍMICA</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>EXAT1</t>
-        </is>
+          <t>CALINST2</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="81">
@@ -2755,26 +2752,23 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
+          <t>QUÍMICA</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>30</v>
+          <t>EXAT2</t>
+        </is>
       </c>
     </row>
     <row r="82">
@@ -2785,23 +2779,26 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
+          <t>QUÍMICA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2263</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PROMTRI1</t>
-        </is>
+          <t>CALEXAT2</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="83">
@@ -2822,16 +2819,13 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>ACTCT1</t>
-        </is>
-      </c>
-      <c r="F83" t="n">
-        <v>20</v>
+          <t>PROMTRI2</t>
+        </is>
       </c>
     </row>
     <row r="84">
@@ -2842,22 +2836,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>TOK: Theory of Knowledge</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>DEBT1</t>
+          <t>ACTCT2</t>
         </is>
       </c>
       <c r="F84" t="n">
@@ -2872,22 +2866,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>TOK: Theory of Knowledge</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>TRAGIT1</t>
+          <t>DEBT2</t>
         </is>
       </c>
       <c r="F85" t="n">
@@ -2902,22 +2896,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>TOK: Theory of Knowledge</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>LECT1</t>
+          <t>TRAGIT2</t>
         </is>
       </c>
       <c r="F86" t="n">
@@ -2932,22 +2926,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>TOK: Theory of Knowledge</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>APT1</t>
+          <t>LECT2</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -2962,26 +2956,26 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>TOK: Theory of Knowledge</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
+          <t>APT2</t>
         </is>
       </c>
       <c r="F88" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89">
@@ -2992,22 +2986,22 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>TOK: Theory of Knowledge</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CALINST1</t>
+          <t>CALINST2</t>
         </is>
       </c>
       <c r="F89" t="n">
@@ -3022,22 +3016,22 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>TOK: Theory of Knowledge</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>EXAT1</t>
+          <t>EXAT2</t>
         </is>
       </c>
     </row>
@@ -3049,22 +3043,22 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>TOK: Theory of Knowledge</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F91" t="n">
@@ -3079,22 +3073,22 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>TOK: Theory of Knowledge</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>PROMTRI1</t>
+          <t>PROMTRI2</t>
         </is>
       </c>
     </row>
@@ -3106,22 +3100,22 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>TOK: Theory of Knowledge</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>ACTCT1</t>
+          <t>ACTCT2</t>
         </is>
       </c>
       <c r="F93" t="n">
@@ -3136,22 +3130,22 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TOK: Theory of Knowledge</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>DEBT1</t>
+          <t>DEBT2</t>
         </is>
       </c>
       <c r="F94" t="n">
@@ -3166,22 +3160,22 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TOK: Theory of Knowledge</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>TRAGIT1</t>
+          <t>TRAGIT2</t>
         </is>
       </c>
       <c r="F95" t="n">
@@ -3196,22 +3190,22 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TOK: Theory of Knowledge</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>LECT1</t>
+          <t>LECT2</t>
         </is>
       </c>
       <c r="F96" t="n">
@@ -3226,22 +3220,22 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>TOK: Theory of Knowledge</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>APT1</t>
+          <t>APT2</t>
         </is>
       </c>
       <c r="F97" t="n">
@@ -3256,22 +3250,22 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>TOK: Theory of Knowledge</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
+          <t>CALINST2</t>
         </is>
       </c>
       <c r="F98" t="n">
@@ -3286,26 +3280,23 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>TOK: Theory of Knowledge</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CALINST1</t>
-        </is>
-      </c>
-      <c r="F99" t="n">
-        <v>70</v>
+          <t>EXAT2</t>
+        </is>
       </c>
     </row>
     <row r="100">
@@ -3316,23 +3307,26 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>TOK: Theory of Knowledge</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>EXAT1</t>
-        </is>
+          <t>CALEXAT2</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="101">
@@ -3343,347 +3337,335 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>TOK: Theory of Knowledge</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2348</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
-        </is>
-      </c>
-      <c r="F101" t="n">
-        <v>30</v>
+          <t>PROMTRI2</t>
+        </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>3BCH-A</t>
+          <t>3BCH-B</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>TOK: Theory of Knowledge</t>
+          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>PROMTRI1</t>
+          <t>INSCUALT2</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>3BCH-A</t>
+          <t>3BCH-B</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Visual Arts NM IB</t>
+          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>ACTCT1</t>
-        </is>
-      </c>
-      <c r="F103" t="n">
-        <v>20</v>
+          <t>EQUINSUT2</t>
+        </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>3BCH-A</t>
+          <t>3BCH-B</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Visual Arts NM IB</t>
+          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>DEBT1</t>
+          <t>CALINST1</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>3BCH-A</t>
+          <t>3BCH-B</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Visual Arts NM IB</t>
+          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>TRAGIT1</t>
+          <t>EQUICALNSUT2</t>
         </is>
       </c>
       <c r="F105" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>3BCH-A</t>
+          <t>3BCH-B</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Visual Arts NM IB</t>
+          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>LECT1</t>
-        </is>
-      </c>
-      <c r="F106" t="n">
-        <v>20</v>
+          <t>EXAT2</t>
+        </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>3BCH-A</t>
+          <t>3BCH-B</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Visual Arts NM IB</t>
+          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>APT1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>3BCH-A</t>
+          <t>3BCH-B</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Visual Arts NM IB</t>
+          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
-        </is>
-      </c>
-      <c r="F108" t="n">
-        <v>70</v>
+          <t>EQUIEXAT2</t>
+        </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>3BCH-A</t>
+          <t>3BCH-B</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Visual Arts NM IB</t>
+          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>CALINST1</t>
-        </is>
-      </c>
-      <c r="F109" t="n">
-        <v>70</v>
+          <t>PROMTRIT2</t>
+        </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>3BCH-A</t>
+          <t>3BCH-B</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Visual Arts NM IB</t>
+          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2243</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>EXAT1</t>
+          <t>EQUICALPROMTR2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>3BCH-A</t>
+          <t>3BCH-B</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Visual Arts NM IB</t>
+          <t>Biología NM IB</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
+          <t>ACTCT2</t>
         </is>
       </c>
       <c r="F111" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>3BCH-A</t>
+          <t>3BCH-B</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Visual Arts NM IB</t>
+          <t>Biología NM IB</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>2348</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PROMTRI1</t>
-        </is>
+          <t>DEBT2</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="113">
@@ -3694,23 +3676,26 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+          <t>Biología NM IB</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>INSCUALT1</t>
-        </is>
+          <t>TRAGIT2</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="114">
@@ -3721,23 +3706,26 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+          <t>Biología NM IB</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>EQUINSUT1</t>
-        </is>
+          <t>LECT2</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="115">
@@ -3748,26 +3736,26 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+          <t>Biología NM IB</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>CALINST1</t>
+          <t>APT2</t>
         </is>
       </c>
       <c r="F115" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="116">
@@ -3778,22 +3766,22 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+          <t>Biología NM IB</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>EQUICALNSUT1</t>
+          <t>SUMAINST2</t>
         </is>
       </c>
       <c r="F116" t="n">
@@ -3808,23 +3796,26 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+          <t>Biología NM IB</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>EXAT1</t>
-        </is>
+          <t>CALINST2</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="118">
@@ -3835,22 +3826,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+          <t>Biología NM IB</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>EQUIEXAT1</t>
+          <t>EXAT2</t>
         </is>
       </c>
     </row>
@@ -3862,22 +3853,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+          <t>Biología NM IB</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F119" t="n">
@@ -3892,26 +3883,23 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+          <t>Biología NM IB</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2298</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>EQUICALEXAT1</t>
-        </is>
-      </c>
-      <c r="F120" t="n">
-        <v>30</v>
+          <t>PROMTRI2</t>
+        </is>
       </c>
     </row>
     <row r="121">
@@ -3922,22 +3910,22 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+          <t>CAS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>PROMTRIT1</t>
+          <t>INSCUALT2</t>
         </is>
       </c>
     </row>
@@ -3949,22 +3937,22 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>ACOMPAÑAMIENTO INTEGRAL EN EL AULA</t>
+          <t>CAS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>2243</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>EQUICALPROMTR1</t>
+          <t>EQUINSUT2</t>
         </is>
       </c>
     </row>
@@ -3976,26 +3964,26 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Biología NM IB</t>
+          <t>CAS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>ACTCT1</t>
+          <t>CALINST1</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="124">
@@ -4006,26 +3994,26 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Biología NM IB</t>
+          <t>CAS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>DEBT1</t>
+          <t>EQUICALNSUT2</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="125">
@@ -4036,26 +4024,23 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Biología NM IB</t>
+          <t>CAS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>TRAGIT1</t>
-        </is>
-      </c>
-      <c r="F125" t="n">
-        <v>20</v>
+          <t>EXAT2</t>
+        </is>
       </c>
     </row>
     <row r="126">
@@ -4066,26 +4051,26 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Biología NM IB</t>
+          <t>CAS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>LECT1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="127">
@@ -4096,26 +4081,23 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Biología NM IB</t>
+          <t>CAS</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>APT1</t>
-        </is>
-      </c>
-      <c r="F127" t="n">
-        <v>20</v>
+          <t>EQUIEXAT2</t>
+        </is>
       </c>
     </row>
     <row r="128">
@@ -4126,26 +4108,23 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Biología NM IB</t>
+          <t>CAS</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
-        </is>
-      </c>
-      <c r="F128" t="n">
-        <v>70</v>
+          <t>PROMTRIT2</t>
+        </is>
       </c>
     </row>
     <row r="129">
@@ -4156,26 +4135,23 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Biología NM IB</t>
+          <t>CAS</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2247</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>CALINST1</t>
-        </is>
-      </c>
-      <c r="F129" t="n">
-        <v>70</v>
+          <t>EQUICALPROMTR2</t>
+        </is>
       </c>
     </row>
     <row r="130">
@@ -4186,22 +4162,22 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Biología NM IB</t>
+          <t>COMPORTAMIENTO</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>EXAT1</t>
+          <t>INSCUALT2</t>
         </is>
       </c>
     </row>
@@ -4213,26 +4189,26 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Biología NM IB</t>
+          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
+          <t>ACTCT2</t>
         </is>
       </c>
       <c r="F131" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132">
@@ -4243,23 +4219,26 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Biología NM IB</t>
+          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>2298</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>PROMTRI1</t>
-        </is>
+          <t>DEBT2</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="133">
@@ -4270,23 +4249,26 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>CAS</t>
+          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>INSCUALT1</t>
-        </is>
+          <t>TRAGIT2</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="134">
@@ -4297,23 +4279,26 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>CAS</t>
+          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>EQUINSUT1</t>
-        </is>
+          <t>LECT2</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="135">
@@ -4324,26 +4309,26 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>CAS</t>
+          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>CALINST1</t>
+          <t>APT2</t>
         </is>
       </c>
       <c r="F135" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="136">
@@ -4354,22 +4339,22 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>CAS</t>
+          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>EQUICALNSUT1</t>
+          <t>SUMAINST1</t>
         </is>
       </c>
       <c r="F136" t="n">
@@ -4384,23 +4369,26 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>CAS</t>
+          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>EXAT1</t>
-        </is>
+          <t>CALINST2</t>
+        </is>
+      </c>
+      <c r="F137" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="138">
@@ -4411,22 +4399,22 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CAS</t>
+          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>EQUIEXAT1</t>
+          <t>EXAT2</t>
         </is>
       </c>
     </row>
@@ -4438,22 +4426,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>CAS</t>
+          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F139" t="n">
@@ -4468,26 +4456,23 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CAS</t>
+          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>EQUICALEXAT1</t>
-        </is>
-      </c>
-      <c r="F140" t="n">
-        <v>30</v>
+          <t>PROMTRI2</t>
+        </is>
       </c>
     </row>
     <row r="141">
@@ -4498,23 +4483,26 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>CAS</t>
+          <t>English B NS IB</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>PROMTRIT1</t>
-        </is>
+          <t>ACTCT2</t>
+        </is>
+      </c>
+      <c r="F141" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="142">
@@ -4525,23 +4513,26 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>CAS</t>
+          <t>English B NS IB</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>2247</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>EQUICALPROMTR1</t>
-        </is>
+          <t>DEBT2</t>
+        </is>
+      </c>
+      <c r="F142" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="143">
@@ -4552,23 +4543,26 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>COMPORTAMIENTO</t>
+          <t>English B NS IB</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>INSCUALT1</t>
-        </is>
+          <t>TRAGIT2</t>
+        </is>
+      </c>
+      <c r="F143" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="144">
@@ -4579,22 +4573,22 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+          <t>English B NS IB</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>ACTCT1</t>
+          <t>LECT2</t>
         </is>
       </c>
       <c r="F144" t="n">
@@ -4609,22 +4603,22 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+          <t>English B NS IB</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>DEBT1</t>
+          <t>APT2</t>
         </is>
       </c>
       <c r="F145" t="n">
@@ -4639,26 +4633,26 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+          <t>English B NS IB</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>TRAGIT1</t>
+          <t>SUMAINST1</t>
         </is>
       </c>
       <c r="F146" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="147">
@@ -4669,26 +4663,26 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+          <t>English B NS IB</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>LECT1</t>
+          <t>CALINST2</t>
         </is>
       </c>
       <c r="F147" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="148">
@@ -4699,26 +4693,23 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+          <t>English B NS IB</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>APT1</t>
-        </is>
-      </c>
-      <c r="F148" t="n">
-        <v>20</v>
+          <t>EXAT2</t>
+        </is>
       </c>
     </row>
     <row r="149">
@@ -4729,26 +4720,26 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+          <t>English B NS IB</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="150">
@@ -4759,26 +4750,23 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+          <t>English B NS IB</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>CALINST1</t>
-        </is>
-      </c>
-      <c r="F150" t="n">
-        <v>70</v>
+          <t>PROMTRI2</t>
+        </is>
       </c>
     </row>
     <row r="151">
@@ -4789,23 +4777,26 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+          <t>FÍSICA</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>EXAT1</t>
-        </is>
+          <t>ACTCT2</t>
+        </is>
+      </c>
+      <c r="F151" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="152">
@@ -4816,26 +4807,26 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+          <t>FÍSICA</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
+          <t>DEBT2</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="153">
@@ -4846,23 +4837,26 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EDUCACIÓN FÍSICA Y PARA LA SALUD</t>
+          <t>FÍSICA</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>PROMTRI1</t>
-        </is>
+          <t>TRAGIT2</t>
+        </is>
+      </c>
+      <c r="F153" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="154">
@@ -4873,22 +4867,22 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>English B NS IB</t>
+          <t>FÍSICA</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>ACTCT1</t>
+          <t>LECT2</t>
         </is>
       </c>
       <c r="F154" t="n">
@@ -4903,22 +4897,22 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>English B NS IB</t>
+          <t>FÍSICA</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>DEBT1</t>
+          <t>APT2</t>
         </is>
       </c>
       <c r="F155" t="n">
@@ -4933,26 +4927,26 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>English B NS IB</t>
+          <t>FÍSICA</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>TRAGIT1</t>
+          <t>SUMAINST1</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="157">
@@ -4963,26 +4957,26 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>English B NS IB</t>
+          <t>FÍSICA</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>LECT1</t>
+          <t>CALINST2</t>
         </is>
       </c>
       <c r="F157" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="158">
@@ -4993,26 +4987,23 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>English B NS IB</t>
+          <t>FÍSICA</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>APT1</t>
-        </is>
-      </c>
-      <c r="F158" t="n">
-        <v>20</v>
+          <t>EXAT2</t>
+        </is>
       </c>
     </row>
     <row r="159">
@@ -5023,26 +5014,26 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>English B NS IB</t>
+          <t>FÍSICA</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="160">
@@ -5053,26 +5044,23 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>English B NS IB</t>
+          <t>FÍSICA</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>CALINST1</t>
-        </is>
-      </c>
-      <c r="F160" t="n">
-        <v>70</v>
+          <t>PROMTRI2</t>
+        </is>
       </c>
     </row>
     <row r="161">
@@ -5083,23 +5071,26 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>English B NS IB</t>
+          <t>History NS IB</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>EXAT1</t>
-        </is>
+          <t>ACTCT2</t>
+        </is>
+      </c>
+      <c r="F161" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="162">
@@ -5110,26 +5101,26 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>English B NS IB</t>
+          <t>History NS IB</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
+          <t>DEBT2</t>
         </is>
       </c>
       <c r="F162" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="163">
@@ -5140,23 +5131,26 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>English B NS IB</t>
+          <t>History NS IB</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>2286</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>PROMTRI1</t>
-        </is>
+          <t>TRAGIT2</t>
+        </is>
+      </c>
+      <c r="F163" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="164">
@@ -5167,22 +5161,22 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>FÍSICA</t>
+          <t>History NS IB</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>ACTCT1</t>
+          <t>LECT2</t>
         </is>
       </c>
       <c r="F164" t="n">
@@ -5197,22 +5191,22 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>FÍSICA</t>
+          <t>History NS IB</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>DEBT1</t>
+          <t>APT2</t>
         </is>
       </c>
       <c r="F165" t="n">
@@ -5227,26 +5221,26 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>FÍSICA</t>
+          <t>History NS IB</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>TRAGIT1</t>
+          <t>SUMAINST1</t>
         </is>
       </c>
       <c r="F166" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="167">
@@ -5257,26 +5251,26 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>FÍSICA</t>
+          <t>History NS IB</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>LECT1</t>
+          <t>CALINST2</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="168">
@@ -5287,26 +5281,23 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>FÍSICA</t>
+          <t>History NS IB</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>APT1</t>
-        </is>
-      </c>
-      <c r="F168" t="n">
-        <v>20</v>
+          <t>EXAT2</t>
+        </is>
       </c>
     </row>
     <row r="169">
@@ -5317,26 +5308,26 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>FÍSICA</t>
+          <t>History NS IB</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F169" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="170">
@@ -5347,26 +5338,23 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>FÍSICA</t>
+          <t>History NS IB</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>CALINST1</t>
-        </is>
-      </c>
-      <c r="F170" t="n">
-        <v>70</v>
+          <t>PROMTRI2</t>
+        </is>
       </c>
     </row>
     <row r="171">
@@ -5377,23 +5365,26 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>FÍSICA</t>
+          <t>Lengua A: Lengua y Literatura NS IB</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>EXAT1</t>
-        </is>
+          <t>ACTCT2</t>
+        </is>
+      </c>
+      <c r="F171" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="172">
@@ -5404,26 +5395,26 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>FÍSICA</t>
+          <t>Lengua A: Lengua y Literatura NS IB</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
+          <t>DEBT2</t>
         </is>
       </c>
       <c r="F172" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="173">
@@ -5434,23 +5425,26 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>FÍSICA</t>
+          <t>Lengua A: Lengua y Literatura NS IB</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>PROMTRI1</t>
-        </is>
+          <t>TRAGIT2</t>
+        </is>
+      </c>
+      <c r="F173" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="174">
@@ -5461,22 +5455,22 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>History NS IB</t>
+          <t>Lengua A: Lengua y Literatura NS IB</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>ACTCT1</t>
+          <t>LECT2</t>
         </is>
       </c>
       <c r="F174" t="n">
@@ -5491,22 +5485,22 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>History NS IB</t>
+          <t>Lengua A: Lengua y Literatura NS IB</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>DEBT1</t>
+          <t>APT2</t>
         </is>
       </c>
       <c r="F175" t="n">
@@ -5521,26 +5515,26 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>History NS IB</t>
+          <t>Lengua A: Lengua y Literatura NS IB</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>TRAGIT1</t>
+          <t>SUMAINST1</t>
         </is>
       </c>
       <c r="F176" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="177">
@@ -5551,26 +5545,26 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>History NS IB</t>
+          <t>Lengua A: Lengua y Literatura NS IB</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>LECT1</t>
+          <t>CALINST2</t>
         </is>
       </c>
       <c r="F177" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="178">
@@ -5581,26 +5575,23 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>History NS IB</t>
+          <t>Lengua A: Lengua y Literatura NS IB</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>APT1</t>
-        </is>
-      </c>
-      <c r="F178" t="n">
-        <v>20</v>
+          <t>EXAT2</t>
+        </is>
       </c>
     </row>
     <row r="179">
@@ -5611,26 +5602,26 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>History NS IB</t>
+          <t>Lengua A: Lengua y Literatura NS IB</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="180">
@@ -5641,26 +5632,23 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>History NS IB</t>
+          <t>Lengua A: Lengua y Literatura NS IB</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2260</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>CALINST1</t>
-        </is>
-      </c>
-      <c r="F180" t="n">
-        <v>70</v>
+          <t>PROMTRI2</t>
+        </is>
       </c>
     </row>
     <row r="181">
@@ -5671,23 +5659,26 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>History NS IB</t>
+          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>EXAT1</t>
-        </is>
+          <t>ACTCT2</t>
+        </is>
+      </c>
+      <c r="F181" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="182">
@@ -5698,26 +5689,26 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>History NS IB</t>
+          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
+          <t>DEBT2</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="183">
@@ -5728,23 +5719,26 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>History NS IB</t>
+          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>2290</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>PROMTRI1</t>
-        </is>
+          <t>TRAGIT2</t>
+        </is>
+      </c>
+      <c r="F183" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="184">
@@ -5755,22 +5749,22 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Lengua A: Lengua y Literatura NS IB</t>
+          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>ACTCT1</t>
+          <t>LECT2</t>
         </is>
       </c>
       <c r="F184" t="n">
@@ -5785,22 +5779,22 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Lengua A: Lengua y Literatura NS IB</t>
+          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>DEBT1</t>
+          <t>APT2</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -5815,26 +5809,26 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Lengua A: Lengua y Literatura NS IB</t>
+          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>TRAGIT1</t>
+          <t>SUMAINST1</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="187">
@@ -5845,26 +5839,26 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Lengua A: Lengua y Literatura NS IB</t>
+          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>LECT1</t>
+          <t>CALINST2</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="188">
@@ -5875,26 +5869,23 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Lengua A: Lengua y Literatura NS IB</t>
+          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>APT1</t>
-        </is>
-      </c>
-      <c r="F188" t="n">
-        <v>20</v>
+          <t>EXAT2</t>
+        </is>
       </c>
     </row>
     <row r="189">
@@ -5905,26 +5896,26 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Lengua A: Lengua y Literatura NS IB</t>
+          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F189" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="190">
@@ -5935,26 +5926,23 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Lengua A: Lengua y Literatura NS IB</t>
+          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>CALINST1</t>
-        </is>
-      </c>
-      <c r="F190" t="n">
-        <v>70</v>
+          <t>PROMTRI2</t>
+        </is>
       </c>
     </row>
     <row r="191">
@@ -5965,23 +5953,26 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Lengua A: Lengua y Literatura NS IB</t>
+          <t>QUÍMICA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>EXAT1</t>
-        </is>
+          <t>ACTCT2</t>
+        </is>
+      </c>
+      <c r="F191" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="192">
@@ -5992,26 +5983,26 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Lengua A: Lengua y Literatura NS IB</t>
+          <t>QUÍMICA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
+          <t>DEBT2</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="193">
@@ -6022,23 +6013,26 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Lengua A: Lengua y Literatura NS IB</t>
+          <t>QUÍMICA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>2260</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>PROMTRI1</t>
-        </is>
+          <t>TRAGIT2</t>
+        </is>
+      </c>
+      <c r="F193" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="194">
@@ -6049,22 +6043,22 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
+          <t>QUÍMICA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>ACTCT1</t>
+          <t>LECT2</t>
         </is>
       </c>
       <c r="F194" t="n">
@@ -6079,22 +6073,22 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
+          <t>QUÍMICA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>DEBT1</t>
+          <t>APT2</t>
         </is>
       </c>
       <c r="F195" t="n">
@@ -6109,26 +6103,26 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
+          <t>QUÍMICA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>TRAGIT1</t>
+          <t>SUMAINST1</t>
         </is>
       </c>
       <c r="F196" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="197">
@@ -6139,26 +6133,26 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
+          <t>QUÍMICA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>LECT1</t>
+          <t>CALINST2</t>
         </is>
       </c>
       <c r="F197" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="198">
@@ -6169,26 +6163,23 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
+          <t>QUÍMICA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>APT1</t>
-        </is>
-      </c>
-      <c r="F198" t="n">
-        <v>20</v>
+          <t>EXAT2</t>
+        </is>
       </c>
     </row>
     <row r="199">
@@ -6199,26 +6190,26 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
+          <t>QUÍMICA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
     </row>
     <row r="200">
@@ -6229,26 +6220,23 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
+          <t>QUÍMICA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2341</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>CALINST1</t>
-        </is>
-      </c>
-      <c r="F200" t="n">
-        <v>70</v>
+          <t>PROMTRI2</t>
+        </is>
       </c>
     </row>
     <row r="201">
@@ -6259,23 +6247,26 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
+          <t>TOK: Theory of Knowledge</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>EXAT1</t>
-        </is>
+          <t>ACTCT2</t>
+        </is>
+      </c>
+      <c r="F201" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="202">
@@ -6286,26 +6277,26 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
+          <t>TOK: Theory of Knowledge</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
+          <t>DEBT2</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="203">
@@ -6316,23 +6307,26 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Matemática: Aplicaciones e Interpretaciones NM IB</t>
+          <t>TOK: Theory of Knowledge</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>PROMTRI1</t>
-        </is>
+          <t>TRAGIT2</t>
+        </is>
+      </c>
+      <c r="F203" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="204">
@@ -6343,22 +6337,22 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>TOK: Theory of Knowledge</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>ACTCT1</t>
+          <t>LECT2</t>
         </is>
       </c>
       <c r="F204" t="n">
@@ -6373,22 +6367,22 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>TOK: Theory of Knowledge</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>DEBT1</t>
+          <t>APT2</t>
         </is>
       </c>
       <c r="F205" t="n">
@@ -6403,26 +6397,26 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>TOK: Theory of Knowledge</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>TRAGIT1</t>
+          <t>CALINST2</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="207">
@@ -6433,26 +6427,23 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>TOK: Theory of Knowledge</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>LECT1</t>
-        </is>
-      </c>
-      <c r="F207" t="n">
-        <v>20</v>
+          <t>EXAT2</t>
+        </is>
       </c>
     </row>
     <row r="208">
@@ -6463,26 +6454,26 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>TOK: Theory of Knowledge</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>APT1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="209">
@@ -6493,26 +6484,23 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>TOK: Theory of Knowledge</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2294</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
-        </is>
-      </c>
-      <c r="F209" t="n">
-        <v>70</v>
+          <t>PROMTRI2</t>
+        </is>
       </c>
     </row>
     <row r="210">
@@ -6523,26 +6511,26 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>CALINST1</t>
+          <t>ACTCT2</t>
         </is>
       </c>
       <c r="F210" t="n">
-        <v>70</v>
+        <v>20</v>
       </c>
     </row>
     <row r="211">
@@ -6553,23 +6541,26 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>EXAT1</t>
-        </is>
+          <t>DEBT2</t>
+        </is>
+      </c>
+      <c r="F211" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="212">
@@ -6580,26 +6571,26 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>CALEXAT1</t>
+          <t>TRAGIT2</t>
         </is>
       </c>
       <c r="F212" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
     </row>
     <row r="213">
@@ -6610,23 +6601,26 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>QUÍMICA</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>2341</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>PROMTRI1</t>
-        </is>
+          <t>LECT2</t>
+        </is>
+      </c>
+      <c r="F213" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="214">
@@ -6637,22 +6631,22 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>TOK: Theory of Knowledge</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>ACTCT1</t>
+          <t>APT2</t>
         </is>
       </c>
       <c r="F214" t="n">
@@ -6667,26 +6661,26 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>TOK: Theory of Knowledge</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>DEBT1</t>
+          <t>SUMAINST1</t>
         </is>
       </c>
       <c r="F215" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="216">
@@ -6697,26 +6691,26 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>TOK: Theory of Knowledge</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>TRAGIT1</t>
+          <t>CALINST2</t>
         </is>
       </c>
       <c r="F216" t="n">
-        <v>20</v>
+        <v>70</v>
       </c>
     </row>
     <row r="217">
@@ -6727,26 +6721,23 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>TOK: Theory of Knowledge</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>LECT1</t>
-        </is>
-      </c>
-      <c r="F217" t="n">
-        <v>20</v>
+          <t>EXAT2</t>
+        </is>
       </c>
     </row>
     <row r="218">
@@ -6757,26 +6748,26 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>TOK: Theory of Knowledge</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>APT1</t>
+          <t>CALEXAT2</t>
         </is>
       </c>
       <c r="F218" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="219">
@@ -6787,433 +6778,22 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>TOK: Theory of Knowledge</t>
+          <t>Visual Arts NM IB</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
-        </is>
-      </c>
-      <c r="F219" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>3BCH-B</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>TOK: Theory of Knowledge</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>2294</t>
-        </is>
-      </c>
-      <c r="D220" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>CALINST1</t>
-        </is>
-      </c>
-      <c r="F220" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>3BCH-B</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>TOK: Theory of Knowledge</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>2294</t>
-        </is>
-      </c>
-      <c r="D221" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>EXAT1</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>3BCH-B</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>TOK: Theory of Knowledge</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>2294</t>
-        </is>
-      </c>
-      <c r="D222" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>CALEXAT1</t>
-        </is>
-      </c>
-      <c r="F222" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>3BCH-B</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>TOK: Theory of Knowledge</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>2294</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>PROMTRI1</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>3BCH-B</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>Visual Arts NM IB</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>2349</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>ACTCT1</t>
-        </is>
-      </c>
-      <c r="F224" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>3BCH-B</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>Visual Arts NM IB</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>2349</t>
-        </is>
-      </c>
-      <c r="D225" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>DEBT1</t>
-        </is>
-      </c>
-      <c r="F225" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>3BCH-B</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>Visual Arts NM IB</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>2349</t>
-        </is>
-      </c>
-      <c r="D226" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>TRAGIT1</t>
-        </is>
-      </c>
-      <c r="F226" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>3BCH-B</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>Visual Arts NM IB</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>2349</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>LECT1</t>
-        </is>
-      </c>
-      <c r="F227" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>3BCH-B</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>Visual Arts NM IB</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>2349</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>APT1</t>
-        </is>
-      </c>
-      <c r="F228" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>3BCH-B</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>Visual Arts NM IB</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>2349</t>
-        </is>
-      </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>SUMAINST1</t>
-        </is>
-      </c>
-      <c r="F229" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>3BCH-B</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>Visual Arts NM IB</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
-        <is>
-          <t>2349</t>
-        </is>
-      </c>
-      <c r="D230" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="E230" t="inlineStr">
-        <is>
-          <t>CALINST1</t>
-        </is>
-      </c>
-      <c r="F230" t="n">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="231">
-      <c r="A231" t="inlineStr">
-        <is>
-          <t>3BCH-B</t>
-        </is>
-      </c>
-      <c r="B231" t="inlineStr">
-        <is>
-          <t>Visual Arts NM IB</t>
-        </is>
-      </c>
-      <c r="C231" t="inlineStr">
-        <is>
-          <t>2349</t>
-        </is>
-      </c>
-      <c r="D231" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>EXAT1</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="A232" t="inlineStr">
-        <is>
-          <t>3BCH-B</t>
-        </is>
-      </c>
-      <c r="B232" t="inlineStr">
-        <is>
-          <t>Visual Arts NM IB</t>
-        </is>
-      </c>
-      <c r="C232" t="inlineStr">
-        <is>
-          <t>2349</t>
-        </is>
-      </c>
-      <c r="D232" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E232" t="inlineStr">
-        <is>
-          <t>CALEXAT1</t>
-        </is>
-      </c>
-      <c r="F232" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="233">
-      <c r="A233" t="inlineStr">
-        <is>
-          <t>3BCH-B</t>
-        </is>
-      </c>
-      <c r="B233" t="inlineStr">
-        <is>
-          <t>Visual Arts NM IB</t>
-        </is>
-      </c>
-      <c r="C233" t="inlineStr">
-        <is>
-          <t>2349</t>
-        </is>
-      </c>
-      <c r="D233" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="E233" t="inlineStr">
-        <is>
-          <t>PROMTRI1</t>
+          <t>PROMTRI2</t>
         </is>
       </c>
     </row>
@@ -35770,7 +35350,7 @@
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>SUMAINST1</t>
+          <t>SUMAINST2</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
@@ -35801,7 +35381,7 @@
       </c>
       <c r="N509" t="inlineStr">
         <is>
-          <t>SUMAINST1 | - | - | - | Sumatoria Insumo 70% T-I</t>
+          <t>SUMAINST2 | - | - | - | Sumatoria Insumo 70% T-I</t>
         </is>
       </c>
     </row>
